--- a/metro.xlsx
+++ b/metro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alenka/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76BA096-DA7A-EB4D-82B9-F5453C0AB6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E8EBCE-2068-C740-9E88-4EBFBBD3F62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20140" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inDC" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="168">
   <si>
     <t>DC</t>
   </si>
@@ -537,6 +537,9 @@
   </si>
   <si>
     <t>trucks</t>
+  </si>
+  <si>
+    <t>include_dc</t>
   </si>
 </sst>
 </file>
@@ -2122,7 +2125,7 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="handling_cost" dataDxfId="45"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="rent_cost" dataDxfId="44"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="fixed" dataDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="include" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="include_dc" dataDxfId="42"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="inventory_turns" dataDxfId="41"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="max_inventory_factor" dataDxfId="40"/>
   </tableColumns>
@@ -2502,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>18</v>

--- a/metro.xlsx
+++ b/metro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alenka/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E8EBCE-2068-C740-9E88-4EBFBBD3F62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D8040A-0AF7-7244-9B91-7AC2C9341624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20140" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inDC" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="170">
   <si>
     <t>DC</t>
   </si>
@@ -541,6 +541,12 @@
   <si>
     <t>include_dc</t>
   </si>
+  <si>
+    <t>param</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
 </sst>
 </file>
 
@@ -731,37 +737,7 @@
     <cellStyle name="Обычный_inStores" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Финансовый [0]_inPeriods" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
-  <dxfs count="58">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="48">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2112,83 +2088,73 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица1" displayName="Таблица1" ref="A1:M8" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица1" displayName="Таблица1" ref="A1:M8" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <autoFilter ref="A1:M8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="DC_id" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DC" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="location" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="dc_lat" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="dc_lon" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="inbound_cost" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="inbound_time" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="handling_cost" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="rent_cost" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="fixed" dataDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="include_dc" dataDxfId="42"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="inventory_turns" dataDxfId="41"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="max_inventory_factor" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="DC_id" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DC" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="location" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="dc_lat" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="dc_lon" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="inbound_cost" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="inbound_time" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="handling_cost" dataDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="rent_cost" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="fixed" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="include_dc" dataDxfId="32"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="inventory_turns" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="max_inventory_factor" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Таблица2" displayName="Таблица2" ref="A1:G53" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Таблица2" displayName="Таблица2" ref="A1:G53" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="A1:G53" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="store_id" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="store" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="store_location" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="store_lat" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="store_lon" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="max_days" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="include" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="store_id" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="store" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="store_location" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="store_lat" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="store_lon" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="max_days" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="include" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Таблица3" displayName="Таблица3" ref="A1:C13" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="26" tableBorderDxfId="25" totalsRowBorderDxfId="24" headerRowCellStyle="Финансовый [0]_inPeriods">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Таблица3" displayName="Таблица3" ref="A1:C13" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14" headerRowCellStyle="Финансовый [0]_inPeriods">
   <autoFilter ref="A1:C13" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="period_id" dataDxfId="23" dataCellStyle="Финансовый [0]_inPeriods"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="period" dataDxfId="22" dataCellStyle="Финансовый [0]_inPeriods"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="include" dataDxfId="21" dataCellStyle="Финансовый [0]_inPeriods"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="period_id" dataDxfId="13" dataCellStyle="Финансовый [0]_inPeriods"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="period" dataDxfId="12" dataCellStyle="Финансовый [0]_inPeriods"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="include" dataDxfId="11" dataCellStyle="Финансовый [0]_inPeriods"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Таблица4" displayName="Таблица4" ref="A1:C598" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Таблица4" displayName="Таблица4" ref="A1:C598" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:C598" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="store_id" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="period_id" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="demand" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="store_id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="period_id" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="demand" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Таблица5" displayName="Таблица5" ref="A1:L2" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L2" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="avg_price" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="container_capacity" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="delay_penalty" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="in_transit_weight" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="max_dc" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="min_distance" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="pallet_size" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="rate" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="rdf" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="tariff" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="truck_capacity" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="truck_speed" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Таблица5" displayName="Таблица5" ref="A1:B13" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B13" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="param" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="value" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -94408,95 +94374,114 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" style="25" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" style="25" customWidth="1"/>
-    <col min="6" max="6" width="15" style="25" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" style="25" customWidth="1"/>
-    <col min="8" max="9" width="9.1640625" style="25"/>
-    <col min="10" max="10" width="11" style="25" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" style="25" customWidth="1"/>
-    <col min="12" max="12" width="14" style="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B2" s="25">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="B3" s="25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="B4" s="25">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="B5" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="B6" s="25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="B7" s="25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="B8" s="25">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="B9" s="25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="B10" s="25">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="B11" s="25">
+        <v>52.47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="B12" s="25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="25">
-        <v>43000</v>
-      </c>
-      <c r="B2" s="25">
-        <v>40</v>
-      </c>
-      <c r="C2" s="25">
-        <v>99999</v>
-      </c>
-      <c r="D2" s="25">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25">
-        <v>99</v>
-      </c>
-      <c r="F2" s="25">
-        <v>50</v>
-      </c>
-      <c r="G2" s="25">
-        <v>1.4</v>
-      </c>
-      <c r="H2" s="25">
-        <v>0.1</v>
-      </c>
-      <c r="I2" s="25">
-        <v>1.25</v>
-      </c>
-      <c r="J2" s="25">
-        <v>52.47</v>
-      </c>
-      <c r="K2" s="25">
-        <v>33</v>
-      </c>
-      <c r="L2" s="25">
+      <c r="B13" s="25">
         <v>500</v>
       </c>
     </row>
